--- a/data/trans_orig/P79A1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79A1_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>500</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>500</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>2460</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>693</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>865</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>865</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>647</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>647</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>647</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>647</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>984</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2129</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2146</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2510,27 +2510,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4521</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>23907</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2818,27 +2818,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13276</t>
+          <t>14733</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,27 +2853,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>33397</t>
+          <t>38639</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31215</t>
+          <t>35943</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>39324</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>685</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>685</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>23907</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>23907</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>23907</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>39324</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>39324</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34003</t>
+          <t>39324</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>27378</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>22604</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>18895</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22292</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>47651</t>
+          <t>53565</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41420</t>
+          <t>46813</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>57330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
